--- a/src/test/java/Util/Book1.xlsx
+++ b/src/test/java/Util/Book1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell Enterprise\eclipse-workspace\Training\src\test\java\Util\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell Enterprise\eclipse-workspace\EdurekaTesting\src\test\java\Util\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22A6F7A-2664-46CB-934A-E1985FDACD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9970D412-1415-4A01-99C4-AF8D3B3A20BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{74444324-F4EB-4D8F-B866-E0B3B3DF004F}"/>
   </bookViews>
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39E00245-479E-4233-8820-90EBD4B64C5A}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -491,153 +491,6 @@
         <v>ymalheroin3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="str">
-        <f>A4&amp;C5</f>
-        <v>hero34</v>
-      </c>
-      <c r="B5" t="str">
-        <f t="shared" ref="B5:B11" si="2">B4&amp;C5</f>
-        <v>heroin34</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" t="str">
-        <f t="shared" si="0"/>
-        <v>hero34@ymail.com</v>
-      </c>
-      <c r="E5" t="str">
-        <f t="shared" si="1"/>
-        <v>ymalheroin34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="str">
-        <f t="shared" ref="A6:A11" si="3">A5&amp;C6</f>
-        <v>hero345</v>
-      </c>
-      <c r="B6" t="str">
-        <f t="shared" si="2"/>
-        <v>heroin345</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6" t="str">
-        <f t="shared" si="0"/>
-        <v>hero345@ymail.com</v>
-      </c>
-      <c r="E6" t="str">
-        <f t="shared" si="1"/>
-        <v>ymalheroin345</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="str">
-        <f t="shared" si="3"/>
-        <v>hero3456</v>
-      </c>
-      <c r="B7" t="str">
-        <f t="shared" si="2"/>
-        <v>heroin3456</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7" t="str">
-        <f t="shared" si="0"/>
-        <v>hero3456@ymail.com</v>
-      </c>
-      <c r="E7" t="str">
-        <f t="shared" si="1"/>
-        <v>ymalheroin3456</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="str">
-        <f t="shared" si="3"/>
-        <v>hero34567</v>
-      </c>
-      <c r="B8" t="str">
-        <f t="shared" si="2"/>
-        <v>heroin34567</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-      <c r="D8" t="str">
-        <f t="shared" si="0"/>
-        <v>hero34567@ymail.com</v>
-      </c>
-      <c r="E8" t="str">
-        <f t="shared" si="1"/>
-        <v>ymalheroin34567</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="str">
-        <f t="shared" si="3"/>
-        <v>hero345678</v>
-      </c>
-      <c r="B9" t="str">
-        <f t="shared" si="2"/>
-        <v>heroin345678</v>
-      </c>
-      <c r="C9">
-        <v>8</v>
-      </c>
-      <c r="D9" t="str">
-        <f t="shared" si="0"/>
-        <v>hero345678@ymail.com</v>
-      </c>
-      <c r="E9" t="str">
-        <f t="shared" si="1"/>
-        <v>ymalheroin345678</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="str">
-        <f t="shared" si="3"/>
-        <v>hero3456789</v>
-      </c>
-      <c r="B10" t="str">
-        <f t="shared" si="2"/>
-        <v>heroin3456789</v>
-      </c>
-      <c r="C10">
-        <v>9</v>
-      </c>
-      <c r="D10" t="str">
-        <f t="shared" si="0"/>
-        <v>hero3456789@ymail.com</v>
-      </c>
-      <c r="E10" t="str">
-        <f t="shared" si="1"/>
-        <v>ymalheroin3456789</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="str">
-        <f t="shared" si="3"/>
-        <v>hero345678910</v>
-      </c>
-      <c r="B11" t="str">
-        <f t="shared" si="2"/>
-        <v>heroin345678910</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-      <c r="D11" t="str">
-        <f t="shared" si="0"/>
-        <v>hero345678910@ymail.com</v>
-      </c>
-      <c r="E11" t="str">
-        <f t="shared" si="1"/>
-        <v>ymalheroin345678910</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
